--- a/reports/livrables/L4_analyse/q2_tableaux.xlsx
+++ b/reports/livrables/L4_analyse/q2_tableaux.xlsx
@@ -1,45 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_promotions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_calendrier" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_remise_par_taux" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_remise_par_taux_exercice" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_remise_par_canal" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_evolution" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_evolution_canal" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_unites_remisees" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_promotions_age" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_promotions_gamme" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_nouveautes_mois_lancement" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_indice_par_promotion" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_comparaison_naive" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_naif_par_exercice" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_naif_par_canal" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_bascules" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_bascules_synthese" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_transitions" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_temoin_par_mois" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_temoin_par_ecart" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_lignes_remisees" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_decomposition_correlation" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_profil_mensuel_magasin" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_resultat_par_groupe_de_mois" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_resultat_par_canal_et_taux" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_registre_des_tests" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_ce_que_rapporte_1_dollar" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_cout_des_remises" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_seuil_par_promotion" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_seuil_contre_observe" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_publicite_et_remises" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_leviers" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_grille_suppression" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="2_promotions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_calendrier" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2_remise_par_taux" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2_remise_par_taux_exercice" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="2_remise_par_canal" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3_evolution" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="3_evolution_canal" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="3_unites_remisees" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="3_promotions_age" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="3_promotions_gamme" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="3_nouveautes_mois_lancement" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="4_indice_par_promotion" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="5_comparaison_naive" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="5_naif_par_exercice" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="5_naif_par_canal" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="6_bascules" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="6_bascules_synthese" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="6_transitions" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="7_temoin_par_mois" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="7_temoin_par_ecart" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="8_lignes_remisees" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="9_decomposition_correlation" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="9_profil_mensuel_magasin" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="9_resultat_par_groupe_de_mois" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="9_resultat_par_canal_et_taux" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="10_registre_des_tests" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="11_ce_que_rapporte_1_dollar" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="11_cout_des_remises" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="11_seuil_par_promotion" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="11_seuil_contre_observe" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="11_publicite_et_remises" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="12_leviers" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="12_grille_suppression" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
